--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513667_FASEFINALBFFB4_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513667_FASEFINALBFFB4_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3574</v>
+        <v>3.9776</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2175</v>
+        <v>2.5668</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1399</v>
+        <v>1.4108</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1372</v>
+        <v>3.1956</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5735</v>
+        <v>2.419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4363</v>
+        <v>0.7766</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7542</v>
+        <v>3.2993</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2971</v>
+        <v>2.7557</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5429</v>
+        <v>0.5436</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.617</v>
+        <v>-0.1037</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7236</v>
+        <v>-0.3367</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1067</v>
+        <v>0.233</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1947</v>
+        <v>1.3632</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1684</v>
+        <v>2.3368</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2721</v>
+        <v>-0.6576</v>
       </c>
       <c r="T2" t="n">
-        <v>0.216</v>
+        <v>-0.6488</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4881</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2976</v>
+        <v>0.0765</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2211</v>
+        <v>0.89</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0765</v>
+        <v>-0.8135</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7899</v>
+        <v>3.5895</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5461</v>
+        <v>2.1687</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2439</v>
+        <v>1.4208</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1956</v>
+        <v>2.3075</v>
       </c>
       <c r="H3" t="n">
-        <v>2.419</v>
+        <v>2.3271</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7766</v>
+        <v>-0.0197</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2993</v>
+        <v>3.1968</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7557</v>
+        <v>3.0508</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5436</v>
+        <v>0.146</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1037</v>
+        <v>-0.8893</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3367</v>
+        <v>-0.7236</v>
       </c>
       <c r="O3" t="n">
-        <v>0.233</v>
+        <v>-0.1657</v>
       </c>
       <c r="P3" t="n">
         <v>1.3632</v>
@@ -688,28 +688,28 @@
         <v>2.3368</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8453</v>
+        <v>-0.0355</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.6695</v>
+        <v>-0.0544</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1757</v>
+        <v>0.0189</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0765</v>
+        <v>-0.0456</v>
       </c>
       <c r="W3" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8135</v>
+        <v>-0.0456</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5247</v>
+        <v>3.1141</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0482</v>
+        <v>2.9185</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4765</v>
+        <v>0.1956</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3075</v>
+        <v>2.1372</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3271</v>
+        <v>2.5735</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0197</v>
+        <v>-0.4363</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1968</v>
+        <v>2.7542</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0508</v>
+        <v>3.2971</v>
       </c>
       <c r="L4" t="n">
-        <v>0.146</v>
+        <v>-0.5429</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8893</v>
+        <v>-0.617</v>
       </c>
       <c r="N4" t="n">
         <v>-0.7236</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1657</v>
+        <v>0.1067</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3632</v>
+        <v>0.1947</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3368</v>
+        <v>1.1684</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1003</v>
+        <v>-0.5155</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1749</v>
+        <v>-0.083</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0746</v>
+        <v>-0.4324</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0456</v>
+        <v>1.2976</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0456</v>
+        <v>0.0765</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. VINALLONGA BLANCO</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7968</v>
+        <v>0.3079</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0233</v>
+        <v>0.3079</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8202</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6655</v>
+        <v>0.3079</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2279</v>
+        <v>0.3079</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8934</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6107</v>
+        <v>0.3079</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4081</v>
+        <v>0.3079</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2026</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2762</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1802</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.096</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9474</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8902</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3397</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5506</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4016</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3079</v>
+        <v>0.1941</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3079</v>
+        <v>-0.2365</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.4306</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3079</v>
+        <v>-0.6655</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3079</v>
+        <v>0.2279</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.8934</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3079</v>
+        <v>0.6107</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3079</v>
+        <v>0.4081</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.2026</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.2762</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.1802</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-1.096</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.9474</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.2875</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.1265</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.4016</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.4016</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2829</v>
+        <v>-0.4957</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1551</v>
+        <v>-1.4107</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.438</v>
+        <v>0.915</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4966</v>
+        <v>-1.1759</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8858</v>
+        <v>-1.0222</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3892</v>
+        <v>-0.1537</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4294</v>
+        <v>-0.6208</v>
       </c>
       <c r="K7" t="n">
-        <v>0.716</v>
+        <v>0.0515</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7134</v>
+        <v>-0.6722</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9328</v>
+        <v>-0.5551</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1698</v>
+        <v>-1.0736</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1026</v>
+        <v>0.5185</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1947</v>
+        <v>1.9474</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1684</v>
+        <v>1.9474</v>
       </c>
       <c r="S7" t="n">
-        <v>1.774</v>
+        <v>-1.0934</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8542</v>
+        <v>-0.7383</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0801</v>
+        <v>-0.3551</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.7482</v>
+        <v>-0.1737</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1547</v>
+        <v>-0.0516</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.5935</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.737</v>
+        <v>-1.2878</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9188</v>
+        <v>0.1454</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6558</v>
+        <v>-1.4332</v>
       </c>
       <c r="G8" t="n">
         <v>0.8731</v>
@@ -1078,13 +1078,13 @@
         <v>1.9474</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2475</v>
+        <v>-0.7983</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6331</v>
+        <v>-0.1403</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8807</v>
+        <v>-0.6581</v>
       </c>
       <c r="V8" t="n">
         <v>-2.3363</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0342</v>
+        <v>-1.3615</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0327</v>
+        <v>1.0208</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9985000000000001</v>
+        <v>-2.3823</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1759</v>
+        <v>0.4966</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0222</v>
+        <v>0.8858</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1537</v>
+        <v>-0.3892</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6208</v>
+        <v>1.4294</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0515</v>
+        <v>0.716</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6722</v>
+        <v>0.7134</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5551</v>
+        <v>-0.9328</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0736</v>
+        <v>0.1698</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5185</v>
+        <v>-1.1026</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9474</v>
+        <v>0.1947</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9474</v>
+        <v>1.1684</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.632</v>
+        <v>0.6954</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3604</v>
+        <v>0.7199</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2716</v>
+        <v>-0.0245</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1737</v>
+        <v>-2.7482</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0516</v>
+        <v>-0.1547</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1221</v>
+        <v>-2.5935</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0771</v>
+        <v>-2.1652</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1724</v>
+        <v>-1.3717</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.7934</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3119</v>
@@ -1234,13 +1234,13 @@
         <v>0.7789</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5441</v>
+        <v>-0.6322</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.263</v>
+        <v>-0.4624</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2811</v>
+        <v>-0.1698</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.414</v>
+        <v>-2.8421</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0026</v>
+        <v>0.4632</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4166</v>
+        <v>-3.3053</v>
       </c>
       <c r="G11" t="n">
         <v>0.1131</v>
@@ -1312,13 +1312,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6955</v>
+        <v>-0.1237</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.371</v>
+        <v>0.0895</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3245</v>
+        <v>-0.2132</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4421</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5887</v>
+        <v>-4.4604</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7894</v>
+        <v>-0.4664</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7992</v>
+        <v>-3.994</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7842</v>
@@ -1390,13 +1390,13 @@
         <v>1.3632</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4852</v>
+        <v>-0.3569</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3867</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0985</v>
+        <v>-0.2933</v>
       </c>
       <c r="V12" t="n">
         <v>-3.7087</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3572</v>
+        <v>-1.4295</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1784</v>
+        <v>6.106</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.535299999999999</v>
+        <v>-7.535400000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>4.493500000000002</v>
+        <v>4.4935</v>
       </c>
       <c r="H13" t="n">
-        <v>6.519699999999999</v>
+        <v>6.5197</v>
       </c>
       <c r="I13" t="n">
         <v>-2.0263</v>
@@ -1468,13 +1468,13 @@
         <v>15.5789</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.1578</v>
+        <v>-3.2302</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1825</v>
+        <v>-1.255</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9751</v>
+        <v>-1.9753</v>
       </c>
       <c r="V13" t="n">
         <v>-10.4821</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4746</v>
+        <v>3.4927</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3581</v>
+        <v>2.2649</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1165</v>
+        <v>1.2278</v>
       </c>
       <c r="G14" t="n">
         <v>-1.8955</v>
@@ -1546,13 +1546,13 @@
         <v>1.1684</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5638</v>
+        <v>1.5819</v>
       </c>
       <c r="T14" t="n">
-        <v>3.449</v>
+        <v>1.3558</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1148</v>
+        <v>0.2261</v>
       </c>
       <c r="V14" t="n">
         <v>3.6116</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.745</v>
+        <v>2.789</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2676</v>
+        <v>3.3673</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-0.5783</v>
       </c>
       <c r="G15" t="n">
         <v>1.6676</v>
@@ -1624,13 +1624,13 @@
         <v>0.7789</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3121</v>
+        <v>-0.2681</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5565</v>
+        <v>-0.4568</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2444</v>
+        <v>0.1887</v>
       </c>
       <c r="V15" t="n">
         <v>0.6105</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8707</v>
+        <v>2.4103</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1389</v>
+        <v>1.3849</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7317</v>
+        <v>1.0253</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.2188</v>
+        <v>-1.6171</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.2761</v>
+        <v>-1.0479</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0573</v>
+        <v>-0.5692</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0255</v>
+        <v>-1.3383</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.5143</v>
+        <v>-0.7953</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4888</v>
+        <v>-0.5429</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1933</v>
+        <v>-0.2788</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7618</v>
+        <v>-0.2526</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4315</v>
+        <v>-0.0262</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1947</v>
+        <v>0.9737</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1684</v>
+        <v>0.9737</v>
       </c>
       <c r="S16" t="n">
-        <v>1.96</v>
+        <v>-0.3816</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3581</v>
+        <v>-0.3295</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6019</v>
+        <v>-0.0522</v>
       </c>
       <c r="V16" t="n">
-        <v>1.9347</v>
+        <v>3.4353</v>
       </c>
       <c r="W16" t="n">
-        <v>1.78</v>
+        <v>3.0526</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1547</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>P. TRUÑO SOMS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8686</v>
+        <v>1.8237</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9497</v>
+        <v>1.8237</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0811</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2846</v>
+        <v>1.8237</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2345</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0501</v>
+        <v>1.8237</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8068</v>
+        <v>1.8237</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9963</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8105</v>
+        <v>1.8237</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5222</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7618</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2396</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5579</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3895</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1419</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8108</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3311</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8679</v>
+        <v>1.1941</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7869</v>
+        <v>2.0526</v>
       </c>
       <c r="F18" t="n">
-        <v>1.081</v>
+        <v>-0.8585</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6171</v>
+        <v>1.2846</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0479</v>
+        <v>0.2345</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5692</v>
+        <v>1.0501</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3383</v>
+        <v>2.8068</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7953</v>
+        <v>1.9963</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5429</v>
+        <v>0.8105</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2788</v>
+        <v>-1.5222</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2526</v>
+        <v>-1.7618</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0262</v>
+        <v>0.2396</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9737</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9737</v>
+        <v>0.3895</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.924</v>
+        <v>1.4674</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9275</v>
+        <v>0.9137</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0035</v>
+        <v>0.5537</v>
       </c>
       <c r="V18" t="n">
-        <v>3.4353</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.0526</v>
+        <v>0.2795</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3826</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. TRUÑO SOMS</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8237</v>
+        <v>1.0216</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8237</v>
+        <v>2.3286</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-1.3069</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8237</v>
+        <v>3.0108</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2.9589</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8237</v>
+        <v>0.0518</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8237</v>
+        <v>5.0475</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>4.4312</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8237</v>
+        <v>0.6163</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-2.0367</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-1.4723</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.5644</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.3477</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.2021</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.1456</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6158</v>
+        <v>0.9524</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6158</v>
+        <v>1.1389</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0.1865</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6158</v>
+        <v>-2.2188</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6158</v>
+        <v>-4.2761</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2.0573</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6158</v>
+        <v>-0.0255</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6158</v>
+        <v>-2.5143</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.4888</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-2.1933</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-1.7618</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.4315</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.1684</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.0417</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.3581</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.6836</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.9347</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.1547</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1267</v>
+        <v>0.6158</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1963</v>
+        <v>0.6158</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0696</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0384</v>
+        <v>0.6158</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1934</v>
+        <v>0.6158</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2318</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0405</v>
+        <v>0.6158</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.6158</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0789</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1934</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2724</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,19 +2092,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1144</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1237</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.009299999999999999</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2812</v>
+        <v>0.4536</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3318</v>
+        <v>0.4954</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.613</v>
+        <v>-0.0418</v>
       </c>
       <c r="G22" t="n">
-        <v>3.0108</v>
+        <v>-0.0384</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9589</v>
+        <v>0.1934</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0518</v>
+        <v>-0.2318</v>
       </c>
       <c r="J22" t="n">
-        <v>5.0475</v>
+        <v>0.0405</v>
       </c>
       <c r="K22" t="n">
-        <v>4.4312</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6163</v>
+        <v>0.0405</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0367</v>
+        <v>-0.0789</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4723</v>
+        <v>0.1934</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5644</v>
+        <v>-0.2724</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.3368</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.921</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5842000000000001</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9550999999999999</v>
+        <v>0.2125</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7946</v>
+        <v>0.1754</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1605</v>
+        <v>0.0371</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4178</v>
+        <v>-0.1469</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7487</v>
+        <v>-0.3936</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1665</v>
+        <v>0.2467</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4429</v>
+        <v>-0.1502</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2177</v>
+        <v>-0.3736</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7748</v>
+        <v>0.2235</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3889</v>
+        <v>0.605</v>
       </c>
       <c r="K23" t="n">
-        <v>2.34</v>
+        <v>0.3618</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0489</v>
+        <v>0.2432</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.946</v>
+        <v>-0.7551</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1223</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8236</v>
+        <v>-0.0197</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3895</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.9737</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1393</v>
+        <v>-0.2441</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5565</v>
+        <v>-0.2722</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6958</v>
+        <v>0.0281</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6105</v>
+        <v>1.2211</v>
       </c>
       <c r="W23" t="n">
-        <v>0.89</v>
+        <v>1.2211</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7126</v>
+        <v>-0.5246</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7923</v>
+        <v>1.9481</v>
       </c>
       <c r="F24" t="n">
-        <v>0.07969999999999999</v>
+        <v>-2.4726</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1502</v>
+        <v>0.4429</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3736</v>
+        <v>1.2177</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2235</v>
+        <v>-0.7748</v>
       </c>
       <c r="J24" t="n">
-        <v>0.605</v>
+        <v>2.3889</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3618</v>
+        <v>2.34</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2432</v>
+        <v>0.0489</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7551</v>
+        <v>-1.946</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-1.1223</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0197</v>
+        <v>-0.8236</v>
       </c>
       <c r="P24" t="n">
+        <v>-0.3895</v>
+      </c>
+      <c r="Q24" t="n">
         <v>-0.9737</v>
       </c>
-      <c r="Q24" t="n">
-        <v>-1.9474</v>
-      </c>
       <c r="R24" t="n">
-        <v>0.9737</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8098</v>
+        <v>0.0325</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.671</v>
+        <v>-0.3572</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1388</v>
+        <v>0.3897</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2211</v>
+        <v>-0.6105</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2211</v>
+        <v>0.89</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.3879</v>
+        <v>-3.52</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7663</v>
+        <v>-3.0654</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6216</v>
+        <v>-0.4546</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1637</v>
@@ -2404,13 +2404,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>0.139</v>
+        <v>0.0069</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2935</v>
+        <v>-0.0055</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1545</v>
+        <v>0.0125</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.236499999999999</v>
+        <v>-8.204800000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.1235</v>
+        <v>-6.4258</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.1129</v>
+        <v>-1.779</v>
       </c>
       <c r="G26" t="n">
         <v>-5.2552</v>
@@ -2482,13 +2482,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6708</v>
+        <v>0.3609</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3064</v>
+        <v>0.3913</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3644</v>
+        <v>-0.0305</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,28 +2515,28 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>2.357000000000003</v>
+        <v>2.356900000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>7.535399999999999</v>
+        <v>7.535399999999998</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.1785</v>
+        <v>-5.1784</v>
       </c>
       <c r="G27" t="n">
-        <v>-4.4935</v>
+        <v>-4.493500000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.5197</v>
+        <v>-6.519699999999998</v>
       </c>
       <c r="I27" t="n">
         <v>2.0262</v>
       </c>
       <c r="J27" t="n">
-        <v>9.465900000000001</v>
+        <v>9.4659</v>
       </c>
       <c r="K27" t="n">
-        <v>4.5192</v>
+        <v>4.519200000000001</v>
       </c>
       <c r="L27" t="n">
         <v>4.9468</v>
@@ -2551,7 +2551,7 @@
         <v>-2.9204</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.789600000000001</v>
+        <v>-7.7896</v>
       </c>
       <c r="Q27" t="n">
         <v>-15.579</v>
@@ -2560,13 +2560,13 @@
         <v>7.789400000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>4.157800000000001</v>
+        <v>4.157700000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>1.975200000000001</v>
+        <v>1.9752</v>
       </c>
       <c r="U27" t="n">
-        <v>2.1826</v>
+        <v>2.1824</v>
       </c>
       <c r="V27" t="n">
         <v>10.4822</v>
